--- a/audit-engine/tests/fixtures-sinteticos/diarios/posicao-2026-08-14.xlsx
+++ b/audit-engine/tests/fixtures-sinteticos/diarios/posicao-2026-08-14.xlsx
@@ -495,10 +495,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>460000</v>
+        <v>500000</v>
       </c>
       <c r="D5">
-        <v>460000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -523,10 +523,10 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="D7">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -623,10 +623,10 @@
         <v>15</v>
       </c>
       <c r="C15">
-        <v>1020000</v>
+        <v>1060000</v>
       </c>
       <c r="D15">
-        <v>1020000</v>
+        <v>1060000</v>
       </c>
     </row>
   </sheetData>
